--- a/data/trans_dic/IP2001-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen caries</t>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 13,47</t>
+          <t>5,64; 14,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 14,99</t>
+          <t>6,19; 15,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 16,53</t>
+          <t>6,7; 16,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 10,05</t>
+          <t>2,84; 9,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,77</t>
+          <t>3,19; 9,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 16,14</t>
+          <t>7,45; 16,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,54</t>
+          <t>6,87; 15,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,86</t>
+          <t>2,28; 9,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 10,31</t>
+          <t>5,22; 10,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 14,47</t>
+          <t>7,61; 14,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 13,95</t>
+          <t>7,68; 14,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,16</t>
+          <t>3,27; 8,18</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,33</t>
+          <t>6,63; 13,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 15,09</t>
+          <t>7,56; 14,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 15,31</t>
+          <t>8,22; 16,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,95</t>
+          <t>2,71; 7,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 13,41</t>
+          <t>6,65; 13,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 12,67</t>
+          <t>6,02; 12,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,64</t>
+          <t>4,7; 10,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,82</t>
+          <t>4,99; 11,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 12,18</t>
+          <t>7,31; 11,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 12,48</t>
+          <t>7,62; 12,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,86</t>
+          <t>7,07; 11,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,97</t>
+          <t>4,68; 9,05</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 11,31</t>
+          <t>3,9; 11,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 14,75</t>
+          <t>6,55; 14,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,18</t>
+          <t>6,32; 13,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,11</t>
+          <t>2,22; 7,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 11,49</t>
+          <t>4,04; 11,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 15,95</t>
+          <t>7,65; 16,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 15,37</t>
+          <t>6,9; 15,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,11</t>
+          <t>2,2; 8,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,54</t>
+          <t>5,02; 9,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,64</t>
+          <t>7,95; 13,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,97</t>
+          <t>7,62; 13,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,18</t>
+          <t>2,59; 6,65</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,77</t>
+          <t>5,35; 11,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 10,2</t>
+          <t>3,86; 10,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 14,32</t>
+          <t>6,64; 14,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,57</t>
+          <t>1,46; 5,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 11,8</t>
+          <t>5,35; 11,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,01</t>
+          <t>4,32; 10,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 15,14</t>
+          <t>7,28; 15,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,8</t>
+          <t>2,73; 9,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,98</t>
+          <t>6,14; 11,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 9,32</t>
+          <t>4,76; 9,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,99; 13,18</t>
+          <t>8,18; 13,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,93</t>
+          <t>2,62; 6,99</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,33</t>
+          <t>6,72; 10,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,02</t>
+          <t>7,74; 11,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,58</t>
+          <t>8,71; 12,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,78</t>
+          <t>3,14; 5,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,72</t>
+          <t>6,46; 9,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,4</t>
+          <t>7,65; 11,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,71</t>
+          <t>7,95; 11,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,86</t>
+          <t>4,47; 7,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,44</t>
+          <t>7,1; 9,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 10,79</t>
+          <t>8,03; 10,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,57</t>
+          <t>8,85; 11,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,48</t>
+          <t>4,19; 6,39</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11595</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13362</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13060</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8221</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16182</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14446</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6936</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>19816</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29544</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27506</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>13384</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>7198; 17880</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8244; 20285</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8288; 20365</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3264; 11343</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4505; 13421</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10593; 23431</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9555; 21759</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3115; 13062</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>14058; 27620</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>20959; 39754</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>20183; 36887</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>8226; 20593</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>17544</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20879</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22539</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9197</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19456</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>19136</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15380</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>37000</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>40015</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>37919</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>28867</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12281; 24436</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14349; 28383</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15990; 31253</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5051; 14675</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13443; 26814</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12771; 26389</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9867; 21757</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12352; 29182</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>28318; 45642</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>30617; 50667</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>28616; 47177</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>20320; 39268</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8946</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14669</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14514</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10138</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17032</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16962</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8334</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>19084</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>31701</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>31476</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>16051</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>5075; 14557</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9478; 20724</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9359; 20389</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4167; 14478</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5607; 15666</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11657; 24595</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11068; 24551</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4046; 14698</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13513; 26179</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>23607; 39979</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>23518; 40764</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9607; 24684</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>16092</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12586</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19069</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5092</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16272</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13607</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21165</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9818</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>32364</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>26193</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>40234</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>14910</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10646; 23235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7394; 20409</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12780; 27675</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2417; 9838</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10444; 23225</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8406; 20975</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>13841; 29293</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4857; 17090</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>24187; 43498</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>18386; 36423</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>31275; 52315</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9003; 23989</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>54177</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61495</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>69182</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28454</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>44758</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>108265</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>127453</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>137136</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>73212</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>43146; 66270</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51020; 77399</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>57365; 83173</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20541; 38987</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>43736; 67227</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>53595; 80425</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>55615; 82868</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>33339; 57334</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>93664; 124699</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>109273; 147774</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>120256; 155821</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>58646; 89442</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2001-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 14,0</t>
+          <t>5,78; 14,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 15,23</t>
+          <t>6,25; 15,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 16,47</t>
+          <t>6,39; 16,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,86</t>
+          <t>2,96; 10,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,49</t>
+          <t>3,42; 9,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,49</t>
+          <t>7,45; 16,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 15,64</t>
+          <t>6,69; 15,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 9,55</t>
+          <t>2,32; 9,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 10,26</t>
+          <t>5,0; 10,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 14,44</t>
+          <t>7,94; 14,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 14,04</t>
+          <t>7,63; 14,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,18</t>
+          <t>3,29; 8,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,2</t>
+          <t>6,67; 13,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 14,96</t>
+          <t>7,77; 15,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 16,06</t>
+          <t>8,42; 15,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,87</t>
+          <t>2,84; 8,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 13,26</t>
+          <t>6,34; 13,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 12,44</t>
+          <t>6,21; 12,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,36</t>
+          <t>4,82; 10,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 11,78</t>
+          <t>5,22; 11,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 11,78</t>
+          <t>7,45; 12,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,61</t>
+          <t>7,53; 12,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 11,66</t>
+          <t>7,26; 11,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 9,05</t>
+          <t>4,77; 9,33</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 11,18</t>
+          <t>3,76; 11,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 14,33</t>
+          <t>6,86; 14,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 13,76</t>
+          <t>6,09; 13,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,72</t>
+          <t>1,83; 7,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,28</t>
+          <t>4,38; 11,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 16,15</t>
+          <t>7,76; 16,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 15,3</t>
+          <t>7,29; 15,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,0</t>
+          <t>2,32; 8,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,73</t>
+          <t>4,98; 10,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,46</t>
+          <t>8,29; 14,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 13,21</t>
+          <t>7,65; 13,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,65</t>
+          <t>2,57; 6,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,68</t>
+          <t>5,24; 12,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,65</t>
+          <t>3,91; 10,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 14,38</t>
+          <t>6,65; 14,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,95</t>
+          <t>1,32; 5,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,91</t>
+          <t>5,43; 12,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,79</t>
+          <t>4,1; 10,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,41</t>
+          <t>8,0; 16,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,61</t>
+          <t>2,86; 10,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 11,04</t>
+          <t>5,9; 10,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 9,43</t>
+          <t>4,87; 9,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 13,68</t>
+          <t>8,13; 13,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,99</t>
+          <t>2,6; 7,06</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,32</t>
+          <t>6,78; 10,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,74</t>
+          <t>7,47; 11,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,62</t>
+          <t>8,7; 12,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,96</t>
+          <t>3,09; 5,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 9,92</t>
+          <t>6,4; 9,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,48</t>
+          <t>7,85; 11,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,84</t>
+          <t>7,93; 11,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,69</t>
+          <t>4,39; 7,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 9,45</t>
+          <t>7,03; 9,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,87</t>
+          <t>8,25; 10,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,47</t>
+          <t>8,8; 11,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,39</t>
+          <t>4,22; 6,41</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7198; 17880</t>
+          <t>7386; 18249</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8244; 20285</t>
+          <t>8328; 20559</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8288; 20365</t>
+          <t>7899; 20166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3264; 11343</t>
+          <t>3411; 11742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4505; 13421</t>
+          <t>4838; 13270</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10593; 23431</t>
+          <t>10589; 22845</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9555; 21759</t>
+          <t>9308; 21721</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3115; 13062</t>
+          <t>3170; 13157</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14058; 27620</t>
+          <t>13451; 27424</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20959; 39754</t>
+          <t>21856; 39581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20183; 36887</t>
+          <t>20051; 37613</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8226; 20593</t>
+          <t>8296; 20927</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12281; 24436</t>
+          <t>12347; 25133</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14349; 28383</t>
+          <t>14730; 28679</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15990; 31253</t>
+          <t>16383; 30618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5051; 14675</t>
+          <t>5291; 15081</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13443; 26814</t>
+          <t>12817; 26809</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12771; 26389</t>
+          <t>13161; 27375</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9867; 21757</t>
+          <t>10117; 22369</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12352; 29182</t>
+          <t>12916; 28208</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28318; 45642</t>
+          <t>28873; 46893</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30617; 50667</t>
+          <t>30252; 50615</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28616; 47177</t>
+          <t>29370; 48149</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20320; 39268</t>
+          <t>20716; 40506</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5075; 14557</t>
+          <t>4892; 14338</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9478; 20724</t>
+          <t>9922; 21274</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9359; 20389</t>
+          <t>9017; 20515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4167; 14478</t>
+          <t>3433; 13256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5607; 15666</t>
+          <t>6081; 16064</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11657; 24595</t>
+          <t>11813; 24570</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11068; 24551</t>
+          <t>11692; 24899</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4046; 14698</t>
+          <t>4268; 15324</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13513; 26179</t>
+          <t>13410; 26970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23607; 39979</t>
+          <t>24610; 41873</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23518; 40764</t>
+          <t>23600; 40396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9607; 24684</t>
+          <t>9551; 23670</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10646; 23235</t>
+          <t>10416; 23926</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7394; 20409</t>
+          <t>7504; 20002</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12780; 27675</t>
+          <t>12805; 27694</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2417; 9838</t>
+          <t>2176; 9810</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10444; 23225</t>
+          <t>10598; 23557</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8406; 20975</t>
+          <t>7966; 20898</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13841; 29293</t>
+          <t>15194; 30862</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4857; 17090</t>
+          <t>5090; 17952</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24187; 43498</t>
+          <t>23236; 41887</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18386; 36423</t>
+          <t>18804; 37769</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31275; 52315</t>
+          <t>31101; 50797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9003; 23989</t>
+          <t>8915; 24244</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43146; 66270</t>
+          <t>43502; 66367</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51020; 77399</t>
+          <t>49264; 74585</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57365; 83173</t>
+          <t>57351; 81317</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20541; 38987</t>
+          <t>20251; 38001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43736; 67227</t>
+          <t>43372; 66992</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53595; 80425</t>
+          <t>54990; 81579</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55615; 82868</t>
+          <t>55501; 82084</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33339; 57334</t>
+          <t>32717; 57977</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93664; 124699</t>
+          <t>92812; 124278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109273; 147774</t>
+          <t>112165; 147484</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120256; 155821</t>
+          <t>119580; 153733</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58646; 89442</t>
+          <t>59127; 89761</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2001-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,08%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,03%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10,56%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 14,29</t>
+          <t>3,33; 9,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 15,44</t>
+          <t>7,08; 16,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 16,31</t>
+          <t>6,57; 15,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 10,2</t>
+          <t>2,43; 9,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,38</t>
+          <t>4,98; 13,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,07</t>
+          <t>6,43; 14,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 15,61</t>
+          <t>6,62; 16,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,62</t>
+          <t>3,08; 10,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,19</t>
+          <t>5,04; 10,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 14,38</t>
+          <t>7,81; 14,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 14,32</t>
+          <t>7,53; 13,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,31</t>
+          <t>3,3; 8,34</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,58%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 13,58</t>
+          <t>6,64; 13,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 15,12</t>
+          <t>6,26; 12,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 15,74</t>
+          <t>4,7; 10,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,09</t>
+          <t>5,03; 11,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 13,26</t>
+          <t>6,8; 13,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 12,91</t>
+          <t>7,78; 15,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,65</t>
+          <t>8,1; 15,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 11,39</t>
+          <t>2,65; 7,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 12,11</t>
+          <t>7,59; 12,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,6</t>
+          <t>7,59; 12,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,9</t>
+          <t>7,26; 11,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,33</t>
+          <t>4,64; 8,93</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,87%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,14%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,8%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,01</t>
+          <t>4,28; 11,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 14,71</t>
+          <t>7,44; 15,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 13,85</t>
+          <t>7,22; 15,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,07</t>
+          <t>2,53; 9,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,57</t>
+          <t>4,13; 11,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,76; 16,13</t>
+          <t>6,63; 14,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 15,52</t>
+          <t>6,59; 14,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,34</t>
+          <t>2,7; 8,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,02</t>
+          <t>4,87; 9,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,1</t>
+          <t>7,81; 13,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 13,09</t>
+          <t>7,75; 12,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,38</t>
+          <t>3,12; 7,22</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,57%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,91%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,03</t>
+          <t>5,56; 11,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,43</t>
+          <t>4,11; 11,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 14,39</t>
+          <t>7,67; 15,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,93</t>
+          <t>2,82; 10,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 12,08</t>
+          <t>4,97; 11,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,75</t>
+          <t>4,05; 10,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 16,24</t>
+          <t>6,62; 14,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 10,09</t>
+          <t>1,34; 6,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 10,63</t>
+          <t>6,25; 10,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,78</t>
+          <t>4,67; 9,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 13,28</t>
+          <t>7,99; 13,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,06</t>
+          <t>2,77; 7,06</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,34</t>
+          <t>6,51; 9,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,31</t>
+          <t>7,68; 11,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,34</t>
+          <t>7,9; 11,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,81</t>
+          <t>4,65; 8,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,89</t>
+          <t>6,75; 10,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,64</t>
+          <t>7,43; 11,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,73</t>
+          <t>8,53; 12,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,77</t>
+          <t>3,31; 6,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 9,42</t>
+          <t>7,11; 9,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 10,84</t>
+          <t>8,13; 10,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,32</t>
+          <t>8,8; 11,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,41</t>
+          <t>4,42; 6,71</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8221</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16182</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14446</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>11595</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>13362</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>13060</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6448</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8221</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16182</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14446</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13001</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7386; 18249</t>
+          <t>4703; 13817</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8328; 20559</t>
+          <t>10068; 22935</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7899; 20166</t>
+          <t>9135; 21616</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3411; 11742</t>
+          <t>2987; 11982</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4838; 13270</t>
+          <t>6360; 17201</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10589; 22845</t>
+          <t>8568; 19968</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9308; 21721</t>
+          <t>8185; 20436</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3170; 13157</t>
+          <t>3672; 12484</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13451; 27424</t>
+          <t>13551; 27742</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21856; 39581</t>
+          <t>21510; 39848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20051; 37613</t>
+          <t>19795; 36651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8296; 20927</t>
+          <t>7986; 20203</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19456</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19136</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15380</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18261</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>17544</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>20879</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>22539</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9197</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19456</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19136</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15380</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28867</t>
+          <t>27082</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12347; 25133</t>
+          <t>13422; 27113</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14730; 28679</t>
+          <t>13276; 26872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16383; 30618</t>
+          <t>9880; 22346</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5291; 15081</t>
+          <t>11623; 27465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12817; 26809</t>
+          <t>12581; 24678</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13161; 27375</t>
+          <t>14754; 28619</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10117; 22369</t>
+          <t>15767; 29782</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12916; 28208</t>
+          <t>4798; 14109</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28873; 46893</t>
+          <t>29381; 47193</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30252; 50615</t>
+          <t>30513; 50159</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29370; 48149</t>
+          <t>29393; 47976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20716; 40506</t>
+          <t>19124; 36815</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10138</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17032</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16962</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8470</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8946</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>14669</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>14514</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7717</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10138</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17032</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16962</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16271</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4892; 14338</t>
+          <t>5940; 15955</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9922; 21274</t>
+          <t>11325; 24289</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9017; 20515</t>
+          <t>11587; 24662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3433; 13256</t>
+          <t>4236; 15140</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6081; 16064</t>
+          <t>5380; 14724</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11813; 24570</t>
+          <t>9592; 21336</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11692; 24899</t>
+          <t>9761; 21015</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4268; 15324</t>
+          <t>4160; 13388</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13410; 26970</t>
+          <t>13107; 25672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24610; 41873</t>
+          <t>23186; 40491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23600; 40396</t>
+          <t>23909; 40015</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9551; 23670</t>
+          <t>10031; 23205</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16272</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13607</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21165</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9588</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>16092</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>12586</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>19069</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5092</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16272</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13607</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21165</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14674</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10416; 23926</t>
+          <t>10845; 23016</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7504; 20002</t>
+          <t>7991; 21393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12805; 27694</t>
+          <t>14577; 28763</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2176; 9810</t>
+          <t>4698; 17052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10598; 23557</t>
+          <t>9892; 23406</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7966; 20898</t>
+          <t>7757; 19562</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15194; 30862</t>
+          <t>12738; 27558</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5090; 17952</t>
+          <t>2203; 11007</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23236; 41887</t>
+          <t>24630; 43260</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18804; 37769</t>
+          <t>18012; 35995</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31101; 50797</t>
+          <t>30554; 50421</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8915; 24244</t>
+          <t>9181; 23376</t>
         </is>
       </c>
     </row>
@@ -2346,37 +2346,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>54177</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>61495</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>69182</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28454</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>54087</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65958</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67954</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>71027</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43502; 66367</t>
+          <t>44124; 65847</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49264; 74585</t>
+          <t>53823; 79914</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57351; 81317</t>
+          <t>55272; 81936</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20251; 38001</t>
+          <t>31994; 56115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43372; 66992</t>
+          <t>43339; 66323</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54990; 81579</t>
+          <t>48968; 72618</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55501; 82084</t>
+          <t>56179; 82855</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32717; 57977</t>
+          <t>20523; 37760</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92812; 124278</t>
+          <t>93753; 124607</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>112165; 147484</t>
+          <t>110538; 146710</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119580; 153733</t>
+          <t>119570; 157149</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59127; 89761</t>
+          <t>57801; 87760</t>
         </is>
       </c>
     </row>
